--- a/activities/Activity-08-Budget-and-Effectiveness-Decision/A08-Budget-and-Effectiveness-Decision-Data.xlsx
+++ b/activities/Activity-08-Budget-and-Effectiveness-Decision/A08-Budget-and-Effectiveness-Decision-Data.xlsx
@@ -8,12 +8,15 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Source Notes" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Options" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Scorecard" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Recommendation" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Source Notes" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="AI Prompt Lab" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Data!$A$1:$G$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Options!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +28,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="94">
+  <si>
+    <t xml:space="preserve">Assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rationale / source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northstar training scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loaded labour rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGD/hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synthetic planning assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual infographic volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eight outputs per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied to base 12-month cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum governance score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum effectiveness score</t>
+  </si>
   <si>
     <t xml:space="preserve">Option</t>
   </si>
@@ -48,64 +111,124 @@
     <t xml:space="preserve">EffectivenessScore</t>
   </si>
   <si>
+    <t xml:space="preserve">MaintenanceSGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataHandlingGate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RightsGate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EditabilityGate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AccessibilityGate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base12MonthCostSGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CostWithContingencySGD</t>
+  </si>
+  <si>
     <t xml:space="preserve">PowerPoint templates</t>
   </si>
   <si>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
     <t xml:space="preserve">PowerPoint + Copilot</t>
   </si>
   <si>
-    <t xml:space="preserve">Mixed tools + PowerPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average AnnualLicenceSGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total AnnualLicenceSGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average TrainingSGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total TrainingSGD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average ProductionHours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total ProductionHours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average ReviewHours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total ReviewHours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average GovernanceScore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total GovernanceScore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decision note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter your evidence-based recommendation here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total EffectivenessScore</t>
+    <t xml:space="preserve">Gemini Notebook + PowerPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed AI tools + PowerPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criterion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WeightPct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effectiveness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source grounding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weighted total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-month cost SGD</t>
   </si>
   <si>
     <t xml:space="preserve">Field</t>
   </si>
   <si>
-    <t xml:space="preserve">Value</t>
+    <t xml:space="preserve">Decision record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferred workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select an eligible option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-month budget SGD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Governance controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reversal trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter evidence that would reverse the decision</t>
   </si>
   <si>
     <t xml:space="preserve">Course</t>
@@ -129,13 +252,64 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">15 August 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
+    <t xml:space="preserve">16 August 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Learner working copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy-ready prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewer / owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using only the attached approved sources, create a source register, identify duplicates or conflicting definitions, clean the table, show formulas or transformations, and return five candidate insights with citations, caveats and a confidence note. Do not invent missing values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter approved sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter checks performed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter edits made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infographic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a one-page executive infographic for Singapore retail managers. Lead with one decision insight, show three supporting metrics, include a five-stage flow and a source footer. Use a clean professional style, strong hierarchy and no invented data. Leave critical labels editable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text to image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a clean vector-like sustainability delivery illustration for a PowerPoint infographic: one electric van, one reusable parcel, a simple route and a feedback symbol. Transparent background, consistent blue/teal/violet/amber palette, no text, no logo, no watermark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemini Notebook deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create Presenter Slides for business stakeholders. Focus on the verified decision insight, use a concise professional style, include source-grounded comparisons and a final recommendation. Avoid claims not supported by selected sources. Download PowerPoint when available; otherwise download PDF and identify what must be rebuilt as editable native PowerPoint objects.</t>
   </si>
 </sst>
 </file>
@@ -191,14 +365,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +388,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7C3AED"/>
+        <bgColor rgb="FF993366"/>
       </patternFill>
     </fill>
   </fills>
@@ -266,8 +445,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -278,20 +461,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -392,7 +571,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF7C3AED"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -591,7 +770,129 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -601,102 +902,258 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="8" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="4" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H2" s="0" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="0" t="str">
+        <f aca="false">IF(AND(F2&gt;=Assumptions!$B$6,G2&gt;=Assumptions!$B$7,I2="PASS",J2="PASS",K2="PASS",L2="PASS"),"Eligible","Not eligible")</f>
+        <v>Not eligible</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <f aca="false">B2+C2+H2+(D2+E2)*Assumptions!$B$3</f>
+        <v>41100</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <f aca="false">N2*(1+Assumptions!$B$5)</f>
+        <v>45210</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>4800</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="3" t="n">
+      <c r="H3" s="0" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="0" t="str">
+        <f aca="false">IF(AND(F3&gt;=Assumptions!$B$6,G3&gt;=Assumptions!$B$7,I3="PASS",J3="PASS",K3="PASS",L3="PASS"),"Eligible","Not eligible")</f>
+        <v>Eligible</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <f aca="false">B3+C3+H3+(D3+E3)*Assumptions!$B$3</f>
+        <v>46050</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">N3*(1+Assumptions!$B$5)</f>
+        <v>50655</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="0" t="str">
+        <f aca="false">IF(AND(F4&gt;=Assumptions!$B$6,G4&gt;=Assumptions!$B$7,I4="PASS",J4="PASS",K4="PASS",L4="PASS"),"Eligible","Not eligible")</f>
+        <v>Eligible</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <f aca="false">B4+C4+H4+(D4+E4)*Assumptions!$B$3</f>
+        <v>42500</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">N4*(1+Assumptions!$B$5)</f>
+        <v>46750</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>9600</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>7200</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>4</v>
+      <c r="G5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="0" t="str">
+        <f aca="false">IF(AND(F5&gt;=Assumptions!$B$6,G5&gt;=Assumptions!$B$7,I5="PASS",J5="PASS",K5="PASS",L5="PASS"),"Eligible","Not eligible")</f>
+        <v>Not eligible</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <f aca="false">B5+C5+H5+(D5+E5)*Assumptions!$B$3</f>
+        <v>54600</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">N5*(1+Assumptions!$B$5)</f>
+        <v>60060</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -708,143 +1165,220 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="24"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <f aca="false">COUNTA(Data!A2:A4)</f>
+      <c r="C6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="0" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <f aca="false">IFERROR(AVERAGE(Data!B2:B4),0)</f>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <f aca="false">SUM(Data!B2:B4)</f>
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <f aca="false">IFERROR(AVERAGE(Data!C2:C4),0)</f>
-        <v>7200</v>
-      </c>
-    </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <f aca="false">SUM(Data!C2:C4)</f>
-        <v>21600</v>
+      <c r="A8" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT($B$2:$B$7,C$2:C$7)/SUM($B$2:$B$7),0)</f>
+        <v>4.2</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT($B$2:$B$7,D$2:D$7)/SUM($B$2:$B$7),0)</f>
+        <v>4.4</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT($B$2:$B$7,E$2:E$7)/SUM($B$2:$B$7),0)</f>
+        <v>4</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT($B$2:$B$7,F$2:F$7)/SUM($B$2:$B$7),0)</f>
+        <v>3.65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <f aca="false">IFERROR(AVERAGE(Data!D2:D4),0)</f>
-        <v>330</v>
+      <c r="A9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="0" t="str">
+        <f aca="false">INDEX(Options!$M$2:$M$5,MATCH(C$1,Options!$A$2:$A$5,0))</f>
+        <v>Not eligible</v>
+      </c>
+      <c r="D9" s="0" t="str">
+        <f aca="false">INDEX(Options!$M$2:$M$5,MATCH(D$1,Options!$A$2:$A$5,0))</f>
+        <v>Eligible</v>
+      </c>
+      <c r="E9" s="0" t="str">
+        <f aca="false">INDEX(Options!$M$2:$M$5,MATCH(E$1,Options!$A$2:$A$5,0))</f>
+        <v>Eligible</v>
+      </c>
+      <c r="F9" s="0" t="str">
+        <f aca="false">INDEX(Options!$M$2:$M$5,MATCH(F$1,Options!$A$2:$A$5,0))</f>
+        <v>Not eligible</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false">SUM(Data!D2:D4)</f>
-        <v>990</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false">IFERROR(AVERAGE(Data!E2:E4),0)</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <f aca="false">SUM(Data!E2:E4)</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <f aca="false">IFERROR(AVERAGE(Data!F2:F4),0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <f aca="false">SUM(Data!F2:F4)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="0" t="n">
-        <f aca="false">SUM(Data!G2:G4)</f>
-        <v>12</v>
+      <c r="A10" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <f aca="false">INDEX(Options!$O$2:$O$5,MATCH(C$1,Options!$A$2:$A$5,0))</f>
+        <v>45210</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <f aca="false">INDEX(Options!$O$2:$O$5,MATCH(D$1,Options!$A$2:$A$5,0))</f>
+        <v>50655</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <f aca="false">INDEX(Options!$O$2:$O$5,MATCH(E$1,Options!$A$2:$A$5,0))</f>
+        <v>46750</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">INDEX(Options!$O$2:$O$5,MATCH(F$1,Options!$A$2:$A$5,0))</f>
+        <v>60060</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +1392,112 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <f aca="false">IFERROR(INDEX(Scorecard!$C$10:$F$10,1,MATCH(B2,Scorecard!$C$1:$F$1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <f aca="false">IFERROR(INDEX(Scorecard!$C$9:$F$9,1,MATCH(B2,Scorecard!$C$1:$F$1,0)),"Check selection")</f>
+        <v>Check selection</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -871,51 +1510,177 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>26</v>
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>36</v>
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
